--- a/artfynd/A 1024-2023 artfynd.xlsx
+++ b/artfynd/A 1024-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1024-2023 artfynd.xlsx
+++ b/artfynd/A 1024-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105903660</v>
+        <v>119300340</v>
       </c>
       <c r="B2" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5445</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 781, Ankarsrums säteri, Sm</t>
+          <t>A 781, Sälden, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578307.1673632096</v>
+        <v>578394</v>
       </c>
       <c r="R2" t="n">
-        <v>6398846.374763555</v>
+        <v>6398753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +777,228 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Susanne Hernqvist, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>105903660</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 781, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>578307</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6398846</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105903668</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91867</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 781, Ankarsrums säteri, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578403</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398744</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
